--- a/diseases/d006/2015-2019.xlsx
+++ b/diseases/d006/2015-2019.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -26346,7 +26346,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -30362,7 +30362,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -33411,7 +33411,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -35493,7 +35493,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -36460,7 +36460,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37575,7 +37575,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -38542,7 +38542,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -39509,7 +39509,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40624,7 +40624,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -41591,7 +41591,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -42558,7 +42558,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -43673,7 +43673,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -44640,7 +44640,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47689,7 +47689,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49771,7 +49771,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -50738,7 +50738,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -51705,7 +51705,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -52820,7 +52820,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -53787,7 +53787,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -54902,7 +54902,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -55869,7 +55869,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -56836,7 +56836,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -57951,7 +57951,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -58918,7 +58918,7 @@
       </c>
       <c r="AJ364" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK364" t="inlineStr">
@@ -59885,7 +59885,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -61000,7 +61000,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">

--- a/diseases/d006/2015-2019.xlsx
+++ b/diseases/d006/2015-2019.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -26346,7 +26346,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -30362,7 +30362,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -33411,7 +33411,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -35493,7 +35493,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -36460,7 +36460,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37575,7 +37575,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -38542,7 +38542,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -39509,7 +39509,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40624,7 +40624,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -41591,7 +41591,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -42558,7 +42558,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -43673,7 +43673,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -44640,7 +44640,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47689,7 +47689,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49771,7 +49771,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -50738,7 +50738,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -51705,7 +51705,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -52820,7 +52820,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -53787,7 +53787,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -54902,7 +54902,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -55869,7 +55869,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -56836,7 +56836,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -57951,7 +57951,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -58918,7 +58918,7 @@
       </c>
       <c r="AJ364" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK364" t="inlineStr">
@@ -59885,7 +59885,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -61000,7 +61000,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">

--- a/diseases/d006/2015-2019.xlsx
+++ b/diseases/d006/2015-2019.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -26346,7 +26346,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -30362,7 +30362,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -33411,7 +33411,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -35493,7 +35493,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -36460,7 +36460,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37575,7 +37575,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -38542,7 +38542,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -39509,7 +39509,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40624,7 +40624,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -41591,7 +41591,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -42558,7 +42558,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -43673,7 +43673,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -44640,7 +44640,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47689,7 +47689,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49771,7 +49771,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -50738,7 +50738,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -51705,7 +51705,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -52820,7 +52820,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -53787,7 +53787,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -54902,7 +54902,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -55869,7 +55869,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -56836,7 +56836,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -57951,7 +57951,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -58918,7 +58918,7 @@
       </c>
       <c r="AJ364" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK364" t="inlineStr">
@@ -59885,7 +59885,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -61000,7 +61000,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">

--- a/diseases/d006/2015-2019.xlsx
+++ b/diseases/d006/2015-2019.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -26346,7 +26346,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -30362,7 +30362,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -33411,7 +33411,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -35493,7 +35493,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -36460,7 +36460,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37575,7 +37575,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -38542,7 +38542,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -39509,7 +39509,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40624,7 +40624,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -41591,7 +41591,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -42558,7 +42558,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -43673,7 +43673,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -44640,7 +44640,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47689,7 +47689,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49771,7 +49771,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -50738,7 +50738,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -51705,7 +51705,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -52820,7 +52820,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -53787,7 +53787,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -54902,7 +54902,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -55869,7 +55869,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -56836,7 +56836,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -57951,7 +57951,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -58918,7 +58918,7 @@
       </c>
       <c r="AJ364" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK364" t="inlineStr">
@@ -59885,7 +59885,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -61000,7 +61000,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">

--- a/diseases/d006/2015-2019.xlsx
+++ b/diseases/d006/2015-2019.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -26346,7 +26346,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -30362,7 +30362,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -33411,7 +33411,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -35493,7 +35493,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -36460,7 +36460,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37575,7 +37575,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -38542,7 +38542,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -39509,7 +39509,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40624,7 +40624,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -41591,7 +41591,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -42558,7 +42558,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -43673,7 +43673,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -44640,7 +44640,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47689,7 +47689,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49771,7 +49771,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -50738,7 +50738,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -51705,7 +51705,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -52820,7 +52820,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -53787,7 +53787,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -54902,7 +54902,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -55869,7 +55869,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -56836,7 +56836,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -57951,7 +57951,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -58918,7 +58918,7 @@
       </c>
       <c r="AJ364" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK364" t="inlineStr">
@@ -59885,7 +59885,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -61000,7 +61000,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">

--- a/diseases/d006/2015-2019.xlsx
+++ b/diseases/d006/2015-2019.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -26346,7 +26346,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -30362,7 +30362,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -33411,7 +33411,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -35493,7 +35493,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -36460,7 +36460,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37575,7 +37575,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -38542,7 +38542,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -39509,7 +39509,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40624,7 +40624,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -41591,7 +41591,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -42558,7 +42558,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -43673,7 +43673,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -44640,7 +44640,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47689,7 +47689,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49771,7 +49771,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -50738,7 +50738,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -51705,7 +51705,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -52820,7 +52820,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -53787,7 +53787,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -54902,7 +54902,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -55869,7 +55869,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -56836,7 +56836,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -57951,7 +57951,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -58918,7 +58918,7 @@
       </c>
       <c r="AJ364" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK364" t="inlineStr">
@@ -59885,7 +59885,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -61000,7 +61000,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
